--- a/impact.xlsx
+++ b/impact.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4F6F14-DB75-4B12-AE0B-3D3D060ABD6D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CA506A-F84E-4D20-8437-9D37BADE0A2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6640" xr2:uid="{9F4004D4-A1D9-4A72-950D-807AD9ECE5A0}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t>Process</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>m3.km</t>
+  </si>
+  <si>
+    <t>Waste collection</t>
   </si>
 </sst>
 </file>
@@ -508,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9A6E0B-B9EE-48A8-800F-BDEF0A29E888}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.1796875" customWidth="1"/>
@@ -557,103 +560,103 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1.38914</v>
+      </c>
+      <c r="D4">
+        <v>4.6600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3">
-        <v>16.03</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="3">
-        <v>50</v>
-      </c>
-      <c r="D6" s="3">
-        <v>20</v>
-      </c>
-      <c r="H6" s="3"/>
+        <v>16.03</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D7" s="3">
-        <v>12</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="3">
-        <v>240</v>
+        <v>130.9</v>
       </c>
       <c r="D8" s="3">
-        <v>5</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="3">
+        <v>240</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3">
         <v>125</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D10" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>0.23535</v>
-      </c>
-      <c r="D11">
-        <v>2.1149999999999999E-2</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -667,27 +670,27 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.23535</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2.1149999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -695,108 +698,108 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>36</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1610</v>
-      </c>
-      <c r="D17" s="3">
-        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1610</v>
+      </c>
+      <c r="D18" s="3">
         <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="D18">
-        <v>2.7799999999999998E-4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="D19">
+        <v>2.7799999999999998E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="D19">
+      <c r="D20">
         <f>0.0003</f>
         <v>2.9999999999999997E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>35</v>
       </c>
-      <c r="C20">
+      <c r="C21">
         <v>0.8</v>
       </c>
-      <c r="D20">
+      <c r="D21">
         <v>1.6999999999999999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="3">
-        <v>-350</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="3">
-        <v>-170</v>
+        <v>-350</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -804,13 +807,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C24" s="3">
+        <v>-170</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -818,10 +821,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -832,15 +835,29 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>28</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>35</v>
       </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
         <v>0</v>
       </c>
     </row>
